--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="402">
   <si>
     <t/>
   </si>
@@ -1202,6 +1202,9 @@
   </si>
   <si>
     <t>IDM AIR MN 8+ BTL500</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
   </si>
   <si>
     <t>20052629</t>
@@ -5273,15 +5276,15 @@
         <v>15</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5298,10 +5301,10 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="398">
   <si>
     <t/>
   </si>
@@ -262,12 +262,6 @@
     <t>BEBELAC UHT CHOC 105</t>
   </si>
   <si>
-    <t>20134336</t>
-  </si>
-  <si>
-    <t>PDIASRE UHT VNILA100</t>
-  </si>
-  <si>
     <t>20046862</t>
   </si>
   <si>
@@ -437,12 +431,6 @@
   </si>
   <si>
     <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>20137777</t>
-  </si>
-  <si>
-    <t>NS/GOODNES HBTSD 189</t>
   </si>
   <si>
     <t>20140174</t>
@@ -1609,7 +1597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F183"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2293,7 +2281,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>34</v>
@@ -2313,7 +2301,7 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -2333,7 +2321,7 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>34</v>
@@ -2353,7 +2341,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>34</v>
@@ -2373,7 +2361,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>34</v>
@@ -2393,7 +2381,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>34</v>
@@ -2413,7 +2401,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>34</v>
@@ -2433,10 +2421,10 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2450,13 +2438,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2473,7 +2461,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>34</v>
@@ -2493,7 +2481,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
@@ -2513,18 +2501,18 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2533,10 +2521,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2553,7 +2541,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>34</v>
@@ -2573,7 +2561,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>34</v>
@@ -2593,7 +2581,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
@@ -2613,7 +2601,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>
@@ -2633,7 +2621,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>34</v>
@@ -2650,10 +2638,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>34</v>
@@ -2673,7 +2661,7 @@
         <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>34</v>
@@ -2693,7 +2681,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>34</v>
@@ -2713,7 +2701,7 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>34</v>
@@ -2733,7 +2721,7 @@
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>
@@ -2753,7 +2741,7 @@
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>34</v>
@@ -2773,7 +2761,7 @@
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>34</v>
@@ -2793,7 +2781,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>34</v>
@@ -2813,7 +2801,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>34</v>
@@ -2833,7 +2821,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2853,7 +2841,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2873,7 +2861,7 @@
         <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2890,10 +2878,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>34</v>
@@ -2910,10 +2898,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2933,7 +2921,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2953,7 +2941,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -2973,7 +2961,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -2993,7 +2981,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -3013,7 +3001,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3033,7 +3021,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3053,7 +3041,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3073,7 +3061,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3090,10 +3078,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3110,10 +3098,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3133,7 +3121,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3153,7 +3141,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3173,7 +3161,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3193,7 +3181,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3213,7 +3201,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3233,7 +3221,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3253,7 +3241,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3270,10 +3258,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3290,13 +3278,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3313,7 +3301,7 @@
         <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>34</v>
@@ -3333,10 +3321,10 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3353,7 +3341,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>34</v>
@@ -3373,10 +3361,10 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3393,7 +3381,7 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>34</v>
@@ -3410,10 +3398,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>12</v>
@@ -3430,13 +3418,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3453,10 +3441,10 @@
         <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3473,10 +3461,10 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3493,7 +3481,7 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>34</v>
@@ -3513,7 +3501,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>34</v>
@@ -3533,7 +3521,7 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>34</v>
@@ -3553,7 +3541,7 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>34</v>
@@ -3573,7 +3561,7 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>34</v>
@@ -3593,7 +3581,7 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>34</v>
@@ -3613,7 +3601,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3633,7 +3621,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3650,10 +3638,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3670,10 +3658,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3693,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3713,7 +3701,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3733,7 +3721,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3753,7 +3741,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3773,10 +3761,10 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3793,10 +3781,10 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3813,10 +3801,10 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3833,10 +3821,10 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3853,10 +3841,10 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3873,10 +3861,10 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3893,10 +3881,10 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3910,13 +3898,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3930,13 +3918,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3953,7 +3941,7 @@
         <v>70</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>34</v>
@@ -3973,7 +3961,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -3993,7 +3981,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4013,7 +4001,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4033,7 +4021,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4053,7 +4041,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4073,18 +4061,18 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4093,18 +4081,18 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4113,10 +4101,10 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4130,13 +4118,13 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>268</v>
+        <v>107</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4150,13 +4138,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>268</v>
+        <v>107</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4173,10 +4161,10 @@
         <v>73</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4193,10 +4181,10 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4213,7 +4201,7 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>34</v>
@@ -4233,10 +4221,10 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4253,10 +4241,10 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4273,10 +4261,10 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>109</v>
+        <v>264</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4293,10 +4281,10 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>109</v>
+        <v>264</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,10 +4301,10 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>268</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4333,10 +4321,10 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>268</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4353,7 +4341,7 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4373,7 +4361,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4393,7 +4381,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4401,39 +4389,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>73</v>
+        <v>297</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>301</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>34</v>
@@ -4450,13 +4438,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4470,13 +4458,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4490,13 +4478,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4510,10 +4498,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
@@ -4530,10 +4518,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4550,13 +4538,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4570,13 +4558,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4590,10 +4578,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4610,10 +4598,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4630,10 +4618,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4650,13 +4638,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4670,70 +4658,70 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>70</v>
+        <v>297</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>326</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>301</v>
+        <v>329</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B155" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>301</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>330</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>34</v>
@@ -4750,10 +4738,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4770,13 +4758,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4790,13 +4778,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4810,10 +4798,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>12</v>
@@ -4830,13 +4818,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4850,13 +4838,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4870,53 +4858,53 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4930,10 +4918,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4950,13 +4938,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4970,70 +4958,70 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>268</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>12</v>
+        <v>364</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>34</v>
@@ -5041,82 +5029,82 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>368</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>34</v>
+        <v>364</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>368</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5130,10 +5118,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>34</v>
@@ -5150,13 +5138,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5170,153 +5158,113 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>109</v>
+        <v>387</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>390</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A184" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A185" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -667,463 +667,466 @@
     <t>FLORIDINA ORANGE 350</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20001119</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK 4+2S</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 200</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 200</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20060210</t>
+  </si>
+  <si>
+    <t>IDM TEH HJAU MLT 330</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20077509</t>
+  </si>
+  <si>
+    <t>IDM LEMON TEA 330ML</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20128561</t>
+  </si>
+  <si>
+    <t>IDM CCNT WTR ORGE250</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20002504</t>
+  </si>
+  <si>
+    <t>ADEM SARI BOX 5'S</t>
+  </si>
+  <si>
+    <t>20141508</t>
+  </si>
+  <si>
+    <t>KRTINGDAENG BDD3X150</t>
+  </si>
+  <si>
+    <t>20121348</t>
+  </si>
+  <si>
+    <t>LASEGAR TWST J-L 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20055226</t>
+  </si>
+  <si>
+    <t>NTRIVE/B  STRWBRY100</t>
+  </si>
+  <si>
+    <t>20082247</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL ORG 100</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20115157</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE 1L</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20067201</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGO TPK 1L</t>
+  </si>
+  <si>
+    <t>20067200</t>
+  </si>
+  <si>
+    <t>BUAVITA GUAVA TPK 1L</t>
+  </si>
+  <si>
+    <t>20116490</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 1L</t>
+  </si>
+  <si>
+    <t>20127835</t>
+  </si>
+  <si>
+    <t>ALANG SARI JN 300ML</t>
+  </si>
+  <si>
+    <t>20130801</t>
+  </si>
+  <si>
+    <t>C/BDK PENYEGAR 350ML</t>
+  </si>
+  <si>
+    <t>10008581</t>
+  </si>
+  <si>
+    <t>C/BDK PENYEGAR 500ML</t>
+  </si>
+  <si>
+    <t>20134246</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 350ML</t>
+  </si>
+  <si>
+    <t>20037153</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 500ML</t>
+  </si>
+  <si>
+    <t>20008785</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRL 1500ML</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20137992</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 1600ML</t>
+  </si>
+  <si>
+    <t>20139457</t>
+  </si>
+  <si>
+    <t>AQUVIVA 12X250ML</t>
+  </si>
+  <si>
+    <t>20126648</t>
+  </si>
+  <si>
+    <t>LE MINERALE 6X330ML</t>
+  </si>
+  <si>
+    <t>20094171</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR 24X200</t>
+  </si>
+  <si>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
+  </si>
+  <si>
+    <t>10004337</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR/MN1500</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>20141623</t>
   </si>
   <si>
     <t>IDM AIR BDD 6X500ML</t>
   </si>
   <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20001119</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK 4+2S</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 200</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 200</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20060210</t>
-  </si>
-  <si>
-    <t>IDM TEH HJAU MLT 330</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20077509</t>
-  </si>
-  <si>
-    <t>IDM LEMON TEA 330ML</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20128561</t>
-  </si>
-  <si>
-    <t>IDM CCNT WTR ORGE250</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20002504</t>
-  </si>
-  <si>
-    <t>ADEM SARI BOX 5'S</t>
-  </si>
-  <si>
-    <t>20141508</t>
-  </si>
-  <si>
-    <t>KRTINGDAENG BDD3X150</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20121348</t>
-  </si>
-  <si>
-    <t>LASEGAR TWST J-L 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20055226</t>
-  </si>
-  <si>
-    <t>NTRIVE/B  STRWBRY100</t>
-  </si>
-  <si>
-    <t>20082247</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL ORG 100</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20115157</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE 1L</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20067201</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGO TPK 1L</t>
-  </si>
-  <si>
-    <t>20067200</t>
-  </si>
-  <si>
-    <t>BUAVITA GUAVA TPK 1L</t>
-  </si>
-  <si>
-    <t>20116490</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 1L</t>
-  </si>
-  <si>
-    <t>20127835</t>
-  </si>
-  <si>
-    <t>ALANG SARI JN 300ML</t>
-  </si>
-  <si>
-    <t>20130801</t>
-  </si>
-  <si>
-    <t>C/BDK PENYEGAR 350ML</t>
-  </si>
-  <si>
-    <t>10008581</t>
-  </si>
-  <si>
-    <t>C/BDK PENYEGAR 500ML</t>
-  </si>
-  <si>
-    <t>20134246</t>
-  </si>
-  <si>
-    <t>KAKI3 PENYEGAR 350ML</t>
-  </si>
-  <si>
-    <t>20037153</t>
-  </si>
-  <si>
-    <t>KAKI3 PENYEGAR 500ML</t>
-  </si>
-  <si>
-    <t>20008785</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRL 1500ML</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20137992</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 1600ML</t>
-  </si>
-  <si>
-    <t>20139457</t>
-  </si>
-  <si>
-    <t>AQUVIVA 12X250ML</t>
-  </si>
-  <si>
-    <t>20126648</t>
-  </si>
-  <si>
-    <t>LE MINERALE 6X330ML</t>
-  </si>
-  <si>
-    <t>20094171</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR 24X200</t>
-  </si>
-  <si>
-    <t>10000426</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL1500</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
-  </si>
-  <si>
-    <t>10004337</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR/MN1500</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>10004336</t>
@@ -1132,9 +1135,6 @@
     <t>INDOMARET AIR MIN600</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>20005529</t>
   </si>
   <si>
@@ -1150,7 +1150,7 @@
     <t>20090527</t>
   </si>
   <si>
-    <t>CRYSTALIN BTL 600ML</t>
+    <t>CRYSTALIN BTL 600mL</t>
   </si>
   <si>
     <t>20008767</t>
@@ -3481,7 +3481,7 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>34</v>
@@ -3501,7 +3501,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>34</v>
@@ -3521,7 +3521,7 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>34</v>
@@ -3541,7 +3541,7 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>34</v>
@@ -3561,7 +3561,7 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>34</v>
@@ -3581,7 +3581,7 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>34</v>
@@ -3601,7 +3601,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3609,19 +3609,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3629,10 +3629,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3641,7 +3641,7 @@
         <v>37</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3649,10 +3649,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3661,7 +3661,7 @@
         <v>37</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3669,10 +3669,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3681,7 +3681,7 @@
         <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3701,7 +3701,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3721,7 +3721,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3729,10 +3729,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3741,18 +3741,18 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3761,7 +3761,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>107</v>
@@ -3769,10 +3769,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3781,7 +3781,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>107</v>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3801,18 +3801,18 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3821,7 +3821,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>34</v>
@@ -3829,10 +3829,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3841,18 +3841,18 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3861,7 +3861,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>5</v>
@@ -3869,30 +3869,30 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3901,7 +3901,7 @@
         <v>70</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>34</v>
@@ -3909,10 +3909,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3921,7 +3921,7 @@
         <v>70</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>34</v>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3941,7 +3941,7 @@
         <v>70</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>34</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3961,7 +3961,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -3969,10 +3969,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3981,7 +3981,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4001,7 +4001,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4009,10 +4009,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4021,7 +4021,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4029,10 +4029,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4041,18 +4041,18 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>34</v>
+        <v>263</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4061,18 +4061,18 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4081,38 +4081,38 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>264</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4121,7 +4121,7 @@
         <v>73</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>107</v>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4141,18 +4141,18 @@
         <v>73</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4161,7 +4161,7 @@
         <v>73</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>34</v>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4181,7 +4181,7 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>34</v>
@@ -4189,10 +4189,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4201,18 +4201,18 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4221,7 +4221,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>107</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4241,18 +4241,18 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>107</v>
+        <v>263</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4261,18 +4261,18 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4281,18 +4281,18 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>264</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4301,7 +4301,7 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>34</v>
@@ -4309,10 +4309,10 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4321,7 +4321,7 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>34</v>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4341,7 +4341,7 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4361,7 +4361,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>297</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4398,13 +4398,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4418,10 +4418,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>34</v>
@@ -4438,13 +4438,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4458,10 +4458,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>12</v>
@@ -4478,10 +4478,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>12</v>
@@ -4498,10 +4498,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
@@ -4518,13 +4518,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4538,10 +4538,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4558,10 +4558,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4578,10 +4578,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4598,10 +4598,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4618,13 +4618,13 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4638,50 +4638,50 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>297</v>
+        <v>218</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>76</v>
+        <v>324</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>297</v>
+        <v>4</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>326</v>
+        <v>34</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>34</v>
@@ -4698,10 +4698,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>34</v>
@@ -4718,10 +4718,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>34</v>
@@ -4738,13 +4738,13 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4758,10 +4758,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>12</v>
@@ -4778,10 +4778,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>12</v>
@@ -4798,13 +4798,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4818,10 +4818,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4838,33 +4838,33 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4878,10 +4878,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>34</v>
@@ -4898,10 +4898,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4918,13 +4918,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>34</v>
+        <v>263</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4938,33 +4938,33 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>264</v>
+        <v>12</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4978,93 +4978,93 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>34</v>
+        <v>362</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5078,10 +5078,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>34</v>
@@ -5098,10 +5098,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>34</v>
@@ -5118,10 +5118,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>34</v>
@@ -5138,10 +5138,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>107</v>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
   <si>
     <t/>
   </si>
@@ -565,6 +565,12 @@
     <t>N/P MINUMAN LIME 330</t>
   </si>
   <si>
+    <t>20142239</t>
+  </si>
+  <si>
+    <t>N/P MINUMAN LIME 1L</t>
+  </si>
+  <si>
     <t>20025359</t>
   </si>
   <si>
@@ -625,6 +631,27 @@
     <t>POP ICE MANGO 5'S</t>
   </si>
   <si>
+    <t>20140068</t>
+  </si>
+  <si>
+    <t>LARISST JELY LECI135</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140066</t>
+  </si>
+  <si>
+    <t>LARISST JELY MANG135</t>
+  </si>
+  <si>
+    <t>20140067</t>
+  </si>
+  <si>
+    <t>LARISST JELY STRW135</t>
+  </si>
+  <si>
     <t>10003389</t>
   </si>
   <si>
@@ -1205,6 +1232,12 @@
   </si>
   <si>
     <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F183"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2281,7 +2314,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>34</v>
@@ -2301,7 +2334,7 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -2321,7 +2354,7 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>34</v>
@@ -2341,7 +2374,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>34</v>
@@ -2361,7 +2394,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>34</v>
@@ -2381,7 +2414,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>34</v>
@@ -2401,7 +2434,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>34</v>
@@ -2421,7 +2454,7 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>12</v>
@@ -3284,7 +3317,7 @@
         <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3304,7 +3337,7 @@
         <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3364,7 +3397,7 @@
         <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3384,7 +3417,7 @@
         <v>24</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3398,13 +3431,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3421,10 +3454,10 @@
         <v>33</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3441,10 +3474,10 @@
         <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3461,7 +3494,7 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>34</v>
@@ -3481,7 +3514,7 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>34</v>
@@ -3501,18 +3534,18 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>34</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3521,18 +3554,18 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>34</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3541,18 +3574,18 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>34</v>
+        <v>208</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3561,7 +3594,7 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>34</v>
@@ -3569,10 +3602,10 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3581,7 +3614,7 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>34</v>
@@ -3589,10 +3622,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3601,7 +3634,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3618,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3638,10 +3671,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3658,10 +3691,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3678,10 +3711,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>15</v>
+        <v>227</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3689,10 +3722,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3701,7 +3734,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3709,10 +3742,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3721,7 +3754,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3729,10 +3762,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3741,18 +3774,18 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3761,18 +3794,18 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3781,18 +3814,18 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3801,7 +3834,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>34</v>
@@ -3809,10 +3842,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3821,18 +3854,18 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3841,18 +3874,18 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3861,27 +3894,27 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>34</v>
@@ -3889,19 +3922,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>34</v>
@@ -3909,50 +3942,50 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3961,7 +3994,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -3969,10 +4002,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3981,7 +4014,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -3989,10 +4022,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4001,7 +4034,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4009,10 +4042,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4021,7 +4054,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4029,10 +4062,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4041,10 +4074,10 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>263</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4061,10 +4094,10 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>263</v>
+        <v>34</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4081,10 +4114,10 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>263</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4098,13 +4131,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4118,61 +4151,61 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>107</v>
+        <v>272</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4181,18 +4214,18 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4201,7 +4234,7 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>107</v>
@@ -4209,10 +4242,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4221,18 +4254,18 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4241,18 +4274,18 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>263</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4261,18 +4294,18 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>263</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4281,18 +4314,18 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4301,18 +4334,18 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4321,18 +4354,18 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4341,18 +4374,18 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4361,7 +4394,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4369,39 +4402,39 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4409,19 +4442,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>34</v>
@@ -4429,179 +4462,179 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>218</v>
+        <v>73</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>15</v>
+        <v>227</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4609,42 +4642,42 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>218</v>
+        <v>33</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>324</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4658,73 +4691,73 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>327</v>
+        <v>227</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4738,113 +4771,113 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4858,13 +4891,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4878,13 +4911,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4898,13 +4931,13 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4918,33 +4951,33 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>263</v>
+        <v>107</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4958,10 +4991,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>34</v>
@@ -4978,47 +5011,47 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>362</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>4</v>
@@ -5029,19 +5062,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>34</v>
@@ -5049,39 +5082,39 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B174" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>34</v>
@@ -5089,22 +5122,22 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5118,10 +5151,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>34</v>
@@ -5129,42 +5162,42 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
+      <c r="E177" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F177" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="E177" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F177" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5178,93 +5211,193 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>387</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>390</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>393</v>
+        <v>107</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>390</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="E183" s="1" t="s">
+      <c r="B184" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F183" s="1" t="s">
+      <c r="F187" s="1" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="405">
   <si>
     <t/>
   </si>
@@ -823,25 +823,13 @@
     <t>FRUIT TEA FREEZE 350</t>
   </si>
   <si>
-    <t>20060210</t>
-  </si>
-  <si>
-    <t>IDM TEH HJAU MLT 330</t>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20077509</t>
-  </si>
-  <si>
-    <t>IDM LEMON TEA 330ML</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
   </si>
   <si>
     <t>20015838</t>
@@ -1630,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4154,7 +4142,7 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>272</v>
@@ -4171,13 +4159,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>272</v>
+        <v>107</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4191,13 +4179,13 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>272</v>
+        <v>107</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4214,10 +4202,10 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4234,10 +4222,10 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4254,7 +4242,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4274,10 +4262,10 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4294,10 +4282,10 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4314,10 +4302,10 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>107</v>
+        <v>272</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4334,10 +4322,10 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>107</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4354,10 +4342,10 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>272</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4374,10 +4362,10 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>272</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4394,7 +4382,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4414,7 +4402,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4434,7 +4422,7 @@
         <v>73</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>70</v>
+        <v>227</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4451,13 +4439,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4471,10 +4459,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>227</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>34</v>
@@ -4494,10 +4482,10 @@
         <v>227</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4514,10 +4502,10 @@
         <v>227</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4534,10 +4522,10 @@
         <v>227</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4554,7 +4542,7 @@
         <v>227</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4574,7 +4562,7 @@
         <v>227</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>12</v>
@@ -4594,10 +4582,10 @@
         <v>227</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4614,10 +4602,10 @@
         <v>227</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4634,7 +4622,7 @@
         <v>227</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4654,7 +4642,7 @@
         <v>227</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4674,7 +4662,7 @@
         <v>227</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4694,10 +4682,10 @@
         <v>227</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4714,67 +4702,67 @@
         <v>227</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>70</v>
+        <v>227</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>227</v>
+        <v>332</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>227</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>227</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>333</v>
+        <v>34</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4791,10 +4779,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>34</v>
@@ -4811,13 +4799,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4831,13 +4819,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4851,10 +4839,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>12</v>
@@ -4871,13 +4859,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4891,13 +4879,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4911,53 +4899,53 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4971,10 +4959,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4991,13 +4979,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>34</v>
+        <v>272</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5011,70 +4999,70 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>272</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>12</v>
+        <v>367</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>34</v>
@@ -5082,36 +5070,36 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>371</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
@@ -5122,39 +5110,39 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>12</v>
+        <v>367</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>34</v>
@@ -5171,13 +5159,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>371</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5191,10 +5179,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>34</v>
@@ -5211,13 +5199,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5231,113 +5219,113 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>107</v>
+        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>12</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>402</v>
+        <v>107</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5351,52 +5339,12 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F187" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F188" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
   <si>
     <t/>
   </si>
@@ -262,6 +262,12 @@
     <t>BEBELAC UHT CHOC 105</t>
   </si>
   <si>
+    <t>20142466</t>
+  </si>
+  <si>
+    <t>BEBELAC STRAW 105</t>
+  </si>
+  <si>
     <t>20046862</t>
   </si>
   <si>
@@ -604,7 +610,7 @@
     <t>20139700</t>
   </si>
   <si>
-    <t>PRISTINE 8.6  1.5L</t>
+    <t>PRISTINE 8.6+  1.5L</t>
   </si>
   <si>
     <t>20108983</t>
@@ -1144,88 +1150,94 @@
     <t>20</t>
   </si>
   <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
     <t>10004336</t>
   </si>
   <si>
     <t>INDOMARET AIR MIN600</t>
   </si>
   <si>
+    <t>20137991</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 700ML</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>10015532</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 330</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20045052</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN330</t>
+  </si>
+  <si>
+    <t>PT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20087862</t>
+  </si>
+  <si>
+    <t>IDM MNUM DRMON 330ML</t>
+  </si>
+  <si>
+    <t>PT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20089542</t>
+  </si>
+  <si>
+    <t>IDM AIR MN 8+ BTL500</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20052629</t>
+  </si>
+  <si>
+    <t>IDM AIR DGN OKSGN600</t>
+  </si>
+  <si>
+    <t>20077499</t>
+  </si>
+  <si>
+    <t>PRISTINE 8.6+ BTL600</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>20008767</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 600ML</t>
+  </si>
+  <si>
     <t>20005529</t>
   </si>
   <si>
     <t>NESTLE PURE LIFE 600</t>
-  </si>
-  <si>
-    <t>20137991</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 700ML</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
-  </si>
-  <si>
-    <t>10015532</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 330</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20045052</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN330</t>
-  </si>
-  <si>
-    <t>PT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20087862</t>
-  </si>
-  <si>
-    <t>IDM MNUM DRMON 330ML</t>
-  </si>
-  <si>
-    <t>PT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20089542</t>
-  </si>
-  <si>
-    <t>IDM AIR MN 8+ BTL500</t>
-  </si>
-  <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20052629</t>
-  </si>
-  <si>
-    <t>IDM AIR DGN OKSGN600</t>
-  </si>
-  <si>
-    <t>20077499</t>
-  </si>
-  <si>
-    <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2445,7 +2457,7 @@
         <v>70</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2459,13 +2471,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2482,7 +2494,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>34</v>
@@ -2502,7 +2514,7 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>34</v>
@@ -2522,18 +2534,18 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2542,10 +2554,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2562,7 +2574,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>34</v>
@@ -2582,7 +2594,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>34</v>
@@ -2602,7 +2614,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
@@ -2622,7 +2634,7 @@
         <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>
@@ -2642,7 +2654,7 @@
         <v>18</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>34</v>
@@ -2659,10 +2671,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>34</v>
@@ -2682,7 +2694,7 @@
         <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>34</v>
@@ -2702,7 +2714,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>34</v>
@@ -2722,7 +2734,7 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>34</v>
@@ -2742,7 +2754,7 @@
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>
@@ -2762,7 +2774,7 @@
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>34</v>
@@ -2782,7 +2794,7 @@
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>34</v>
@@ -2802,7 +2814,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>34</v>
@@ -2822,7 +2834,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>34</v>
@@ -2842,7 +2854,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2862,7 +2874,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2882,7 +2894,7 @@
         <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2899,10 +2911,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>34</v>
@@ -2922,7 +2934,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2942,7 +2954,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2962,7 +2974,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -2982,7 +2994,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -3002,7 +3014,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -3022,7 +3034,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3042,7 +3054,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3062,7 +3074,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3082,7 +3094,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3099,10 +3111,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3122,7 +3134,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3142,7 +3154,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3162,7 +3174,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3182,7 +3194,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3202,7 +3214,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3222,7 +3234,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3242,7 +3254,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3262,7 +3274,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3279,10 +3291,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3302,7 +3314,7 @@
         <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>34</v>
@@ -3322,10 +3334,10 @@
         <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3342,10 +3354,10 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3362,7 +3374,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>34</v>
@@ -3382,7 +3394,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>34</v>
@@ -3402,10 +3414,10 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3422,10 +3434,10 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3439,13 +3451,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3462,10 +3474,10 @@
         <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3482,10 +3494,10 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3502,7 +3514,7 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>34</v>
@@ -3522,18 +3534,18 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>208</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>209</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3542,10 +3554,10 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3562,10 +3574,10 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3582,10 +3594,10 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3602,7 +3614,7 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>34</v>
@@ -3622,7 +3634,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3642,7 +3654,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3662,7 +3674,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3682,7 +3694,7 @@
         <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3702,7 +3714,7 @@
         <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3710,19 +3722,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3742,7 +3754,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3762,7 +3774,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3782,7 +3794,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3802,7 +3814,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>34</v>
@@ -3822,7 +3834,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>34</v>
@@ -3842,10 +3854,10 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3862,10 +3874,10 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3882,10 +3894,10 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3902,10 +3914,10 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3922,7 +3934,7 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>34</v>
@@ -3942,10 +3954,10 @@
         <v>37</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3962,7 +3974,7 @@
         <v>37</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3979,13 +3991,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4002,7 +4014,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4022,7 +4034,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4042,7 +4054,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4062,7 +4074,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4082,7 +4094,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4102,7 +4114,7 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>34</v>
@@ -4122,7 +4134,7 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>34</v>
@@ -4142,30 +4154,30 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>272</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4182,10 +4194,10 @@
         <v>73</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4202,10 +4214,10 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4222,7 +4234,7 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>34</v>
@@ -4242,7 +4254,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4262,10 +4274,10 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4282,10 +4294,10 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4302,10 +4314,10 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>272</v>
+        <v>109</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4322,10 +4334,10 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4342,10 +4354,10 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>34</v>
+        <v>274</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4362,7 +4374,7 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4382,7 +4394,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4402,7 +4414,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4422,7 +4434,7 @@
         <v>73</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4439,13 +4451,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>229</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4459,13 +4471,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4479,10 +4491,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>34</v>
@@ -4499,13 +4511,13 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -4519,10 +4531,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
@@ -4539,10 +4551,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4559,10 +4571,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>12</v>
@@ -4579,13 +4591,13 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4599,10 +4611,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4619,10 +4631,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4639,10 +4651,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4659,10 +4671,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4679,13 +4691,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,50 +4711,50 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>329</v>
+        <v>76</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>34</v>
@@ -4759,10 +4771,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4779,10 +4791,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>34</v>
@@ -4799,13 +4811,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4819,10 +4831,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>12</v>
@@ -4839,10 +4851,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>12</v>
@@ -4859,13 +4871,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4879,10 +4891,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4899,33 +4911,33 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -4939,10 +4951,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4959,10 +4971,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4979,13 +4991,13 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>272</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -4999,33 +5011,33 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>12</v>
+        <v>274</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>362</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,93 +5051,93 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>367</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>367</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5139,13 +5151,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>34</v>
+        <v>274</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5159,13 +5171,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>34</v>
+        <v>369</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5179,10 +5191,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>34</v>
@@ -5199,13 +5211,13 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5325,7 +5337,7 @@
         <v>21</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5345,6 +5357,46 @@
         <v>24</v>
       </c>
       <c r="F186" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F188" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="411">
   <si>
     <t/>
   </si>
@@ -427,6 +427,12 @@
     <t>L-MEN WP 2GO CHO 200</t>
   </si>
   <si>
+    <t>20135795</t>
+  </si>
+  <si>
+    <t>TS COLLGN PEACH190ML</t>
+  </si>
+  <si>
     <t>20124409</t>
   </si>
   <si>
@@ -451,6 +457,9 @@
     <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>20133540</t>
   </si>
   <si>
@@ -698,9 +707,6 @@
   </si>
   <si>
     <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>14</t>
   </si>
   <si>
     <t>20026226</t>
@@ -1630,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2894,7 +2900,7 @@
         <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2931,10 +2937,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>4</v>
+        <v>148</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2942,10 +2948,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2954,7 +2960,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2962,10 +2968,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2974,7 +2980,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -2982,10 +2988,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2994,7 +3000,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -3002,10 +3008,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -3014,7 +3020,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -3022,10 +3028,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -3034,7 +3040,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3042,10 +3048,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3054,7 +3060,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3062,10 +3068,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3074,7 +3080,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3082,10 +3088,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
@@ -3094,7 +3100,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3102,10 +3108,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3114,7 +3120,7 @@
         <v>24</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3122,19 +3128,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3142,10 +3148,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3154,7 +3160,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3162,10 +3168,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3174,7 +3180,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3182,10 +3188,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3194,7 +3200,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3202,10 +3208,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3214,7 +3220,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3222,10 +3228,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3234,7 +3240,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3242,10 +3248,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3254,7 +3260,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3262,10 +3268,10 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
@@ -3274,7 +3280,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3282,10 +3288,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3294,7 +3300,7 @@
         <v>27</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3302,19 +3308,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>34</v>
@@ -3322,10 +3328,10 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3334,7 +3340,7 @@
         <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>34</v>
@@ -3342,10 +3348,10 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3354,18 +3360,18 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3374,18 +3380,18 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3394,7 +3400,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>34</v>
@@ -3402,10 +3408,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3414,7 +3420,7 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>34</v>
@@ -3422,10 +3428,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3434,18 +3440,18 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3454,38 +3460,38 @@
         <v>30</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3494,18 +3500,18 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3514,18 +3520,18 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3534,7 +3540,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>34</v>
@@ -3542,10 +3548,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3554,10 +3560,10 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>210</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,18 +3580,18 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3594,18 +3600,18 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3614,18 +3620,18 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3634,7 +3640,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3642,10 +3648,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3654,7 +3660,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3662,10 +3668,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3674,7 +3680,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3682,10 +3688,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3694,7 +3700,7 @@
         <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3702,10 +3708,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3714,7 +3720,7 @@
         <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3722,10 +3728,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3734,7 +3740,7 @@
         <v>33</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>229</v>
+        <v>73</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3751,10 +3757,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>148</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3774,7 +3780,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3794,7 +3800,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3814,7 +3820,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>34</v>
@@ -3834,7 +3840,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>34</v>
@@ -3854,7 +3860,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>34</v>
@@ -3874,10 +3880,10 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3894,7 +3900,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>109</v>
@@ -3914,7 +3920,7 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>109</v>
@@ -3934,10 +3940,10 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3954,7 +3960,7 @@
         <v>37</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>34</v>
@@ -3974,10 +3980,10 @@
         <v>37</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,7 +4000,7 @@
         <v>37</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4011,13 +4017,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4034,7 +4040,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4054,7 +4060,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4074,7 +4080,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4094,7 +4100,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4114,7 +4120,7 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>34</v>
@@ -4134,7 +4140,7 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>34</v>
@@ -4154,7 +4160,7 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>34</v>
@@ -4174,30 +4180,30 @@
         <v>70</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>274</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4214,7 +4220,7 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>109</v>
@@ -4234,10 +4240,10 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4254,7 +4260,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4274,7 +4280,7 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>34</v>
@@ -4294,10 +4300,10 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4314,7 +4320,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>109</v>
@@ -4334,10 +4340,10 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>274</v>
+        <v>109</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4354,10 +4360,10 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4374,10 +4380,10 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -4394,7 +4400,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4414,7 +4420,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4434,7 +4440,7 @@
         <v>73</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4454,7 +4460,7 @@
         <v>73</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>229</v>
+        <v>73</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>34</v>
@@ -4471,13 +4477,13 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>229</v>
+        <v>73</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>148</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -4491,13 +4497,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4511,10 +4517,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>34</v>
@@ -4531,13 +4537,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -4551,10 +4557,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4571,10 +4577,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>12</v>
@@ -4591,10 +4597,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>12</v>
@@ -4611,13 +4617,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4631,10 +4637,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4651,10 +4657,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4671,10 +4677,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4691,10 +4697,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>5</v>
@@ -4711,13 +4717,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4731,50 +4737,50 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>229</v>
+        <v>148</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>229</v>
+        <v>73</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>331</v>
+        <v>76</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F156" s="1" t="s">
         <v>333</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4791,10 +4797,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>34</v>
@@ -4811,10 +4817,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>34</v>
@@ -4831,13 +4837,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4851,10 +4857,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>12</v>
@@ -4871,10 +4877,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>12</v>
@@ -4891,13 +4897,13 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4911,10 +4917,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -4931,33 +4937,33 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -4971,10 +4977,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4991,10 +4997,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>34</v>
@@ -5011,13 +5017,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>274</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5031,33 +5037,33 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>12</v>
+        <v>276</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5071,93 +5077,93 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>369</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>274</v>
+        <v>34</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5171,13 +5177,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>369</v>
+        <v>276</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5191,13 +5197,13 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>34</v>
+        <v>371</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5211,10 +5217,10 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>34</v>
@@ -5231,93 +5237,93 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>392</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5331,13 +5337,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>109</v>
+        <v>397</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5351,13 +5357,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5371,13 +5377,13 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
@@ -5391,12 +5397,32 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E188" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F188" s="1" t="s">
+      <c r="F189" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="408">
   <si>
     <t/>
   </si>
@@ -367,18 +367,6 @@
     <t>MILKU SUSU CKLT 200</t>
   </si>
   <si>
-    <t>20133427</t>
-  </si>
-  <si>
-    <t>YOBICK YOG ORIGNL180</t>
-  </si>
-  <si>
-    <t>20133429</t>
-  </si>
-  <si>
-    <t>YOBICK YOG SAKURA180</t>
-  </si>
-  <si>
     <t>10004669</t>
   </si>
   <si>
@@ -586,6 +574,15 @@
     <t>N/P MINUMAN LIME 1L</t>
   </si>
   <si>
+    <t>20142492</t>
+  </si>
+  <si>
+    <t>SPRITE NIPIS MINT1L</t>
+  </si>
+  <si>
+    <t>PT,(E-14H)</t>
+  </si>
+  <si>
     <t>20025359</t>
   </si>
   <si>
@@ -890,12 +887,6 @@
   </si>
   <si>
     <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20128561</t>
-  </si>
-  <si>
-    <t>IDM CCNT WTR ORGE250</t>
   </si>
   <si>
     <t>20009737</t>
@@ -1636,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2657,10 +2648,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>34</v>
@@ -2677,10 +2668,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>34</v>
@@ -2700,7 +2691,7 @@
         <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>34</v>
@@ -2720,7 +2711,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>34</v>
@@ -2740,7 +2731,7 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>34</v>
@@ -2760,7 +2751,7 @@
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>
@@ -2780,7 +2771,7 @@
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>34</v>
@@ -2800,7 +2791,7 @@
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>34</v>
@@ -2820,7 +2811,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>34</v>
@@ -2840,7 +2831,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>34</v>
@@ -2860,7 +2851,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2880,7 +2871,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2900,7 +2891,7 @@
         <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2908,19 +2899,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>34</v>
@@ -2928,19 +2919,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2960,7 +2951,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2980,7 +2971,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -3000,7 +2991,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -3020,7 +3011,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -3040,7 +3031,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3060,7 +3051,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3080,7 +3071,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3100,7 +3091,7 @@
         <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3117,10 +3108,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3137,10 +3128,10 @@
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3160,7 +3151,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3180,7 +3171,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3200,7 +3191,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3220,7 +3211,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3240,7 +3231,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3260,7 +3251,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3280,7 +3271,7 @@
         <v>27</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3297,10 +3288,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3317,10 +3308,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>34</v>
@@ -3340,18 +3331,18 @@
         <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3360,18 +3351,18 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3380,18 +3371,18 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3400,7 +3391,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>34</v>
@@ -3408,10 +3399,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3420,7 +3411,7 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>34</v>
@@ -3428,10 +3419,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3440,18 +3431,18 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3460,38 +3451,38 @@
         <v>30</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3500,18 +3491,18 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3520,18 +3511,18 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3540,7 +3531,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>34</v>
@@ -3548,10 +3539,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3560,18 +3551,18 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>34</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3580,18 +3571,18 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3600,18 +3591,18 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3620,18 +3611,18 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3640,7 +3631,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3648,10 +3639,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3660,7 +3651,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3668,10 +3659,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3680,7 +3671,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3688,10 +3679,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3700,7 +3691,7 @@
         <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3708,10 +3699,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3720,7 +3711,7 @@
         <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3728,10 +3719,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3740,7 +3731,7 @@
         <v>33</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3748,19 +3739,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3768,10 +3759,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3780,7 +3771,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3788,10 +3779,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3800,7 +3791,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3808,10 +3799,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3820,7 +3811,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>34</v>
@@ -3828,10 +3819,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3840,7 +3831,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>34</v>
@@ -3848,10 +3839,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3860,7 +3851,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>34</v>
@@ -3868,10 +3859,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3880,18 +3871,18 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3900,7 +3891,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>109</v>
@@ -3908,10 +3899,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3920,7 +3911,7 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>109</v>
@@ -3928,10 +3919,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3940,18 +3931,18 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3960,7 +3951,7 @@
         <v>37</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>34</v>
@@ -3968,10 +3959,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3980,18 +3971,18 @@
         <v>37</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -4000,7 +3991,7 @@
         <v>37</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -4008,30 +3999,30 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4040,7 +4031,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4048,10 +4039,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4060,7 +4051,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4068,10 +4059,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4080,7 +4071,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4088,10 +4079,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4100,7 +4091,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4108,10 +4099,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4120,7 +4111,7 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>34</v>
@@ -4128,10 +4119,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4140,7 +4131,7 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>34</v>
@@ -4148,10 +4139,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4160,7 +4151,7 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>34</v>
@@ -4168,10 +4159,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4180,38 +4171,38 @@
         <v>70</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>276</v>
+        <v>109</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4220,7 +4211,7 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>109</v>
@@ -4228,10 +4219,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4240,18 +4231,18 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4260,7 +4251,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4268,10 +4259,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4280,7 +4271,7 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>34</v>
@@ -4288,10 +4279,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4300,18 +4291,18 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4320,7 +4311,7 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>109</v>
@@ -4328,10 +4319,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4340,18 +4331,18 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>109</v>
+        <v>275</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4360,18 +4351,18 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4380,18 +4371,18 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4400,7 +4391,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4408,10 +4399,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4420,7 +4411,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4428,10 +4419,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4440,7 +4431,7 @@
         <v>73</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4448,39 +4439,39 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>34</v>
@@ -4488,79 +4479,79 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4568,19 +4559,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>12</v>
@@ -4588,59 +4579,59 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4648,19 +4639,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4668,19 +4659,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4688,99 +4679,99 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>5</v>
+        <v>330</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>148</v>
+        <v>333</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>148</v>
+        <v>333</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>333</v>
+        <v>34</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4788,19 +4779,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>34</v>
@@ -4808,59 +4799,59 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>12</v>
@@ -4868,119 +4859,119 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4988,99 +4979,99 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>12</v>
+        <v>368</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>34</v>
@@ -5088,36 +5079,36 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>371</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
@@ -5128,10 +5119,10 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
@@ -5140,227 +5131,227 @@
         <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>12</v>
+        <v>275</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>371</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B180" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>34</v>
+        <v>391</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>12</v>
+        <v>394</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>400</v>
+        <v>109</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>397</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>109</v>
@@ -5368,61 +5359,21 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A189" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F189" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="407">
   <si>
     <t/>
   </si>
@@ -580,9 +580,6 @@
     <t>SPRITE NIPIS MINT1L</t>
   </si>
   <si>
-    <t>PT,(E-14H)</t>
-  </si>
-  <si>
     <t>20025359</t>
   </si>
   <si>
@@ -775,13 +772,13 @@
     <t>20102789</t>
   </si>
   <si>
-    <t>ABC CHOCMLT COFF 200</t>
+    <t>ABC CHOCMLT COFF 180</t>
   </si>
   <si>
     <t>20102790</t>
   </si>
   <si>
-    <t>ABC MILK COFFEE 200</t>
+    <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
     <t>20036157</t>
@@ -3334,15 +3331,15 @@
         <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>189</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3359,10 +3356,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3379,10 +3376,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3399,10 +3396,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3419,10 +3416,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3439,10 +3436,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3459,10 +3456,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3479,10 +3476,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3499,10 +3496,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3519,10 +3516,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>208</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3539,10 +3536,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3554,15 +3551,15 @@
         <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3574,15 +3571,15 @@
         <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>215</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3594,15 +3591,15 @@
         <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3619,10 +3616,10 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>219</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3639,10 +3636,10 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3659,10 +3656,10 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>224</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3679,10 +3676,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>226</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3699,10 +3696,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>228</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3719,10 +3716,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>229</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>230</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3739,10 +3736,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>231</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>232</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3759,10 +3756,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3779,10 +3776,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3799,10 +3796,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3819,10 +3816,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3839,10 +3836,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>242</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3859,10 +3856,10 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>244</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3879,10 +3876,10 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3899,10 +3896,10 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3919,10 +3916,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>250</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3939,10 +3936,10 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3959,10 +3956,10 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -3979,10 +3976,10 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3999,10 +3996,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4019,10 +4016,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4039,10 +4036,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4059,10 +4056,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4079,10 +4076,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4099,10 +4096,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4119,10 +4116,10 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4139,10 +4136,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>272</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4159,10 +4156,10 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>274</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
@@ -4174,15 +4171,15 @@
         <v>33</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>277</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4199,10 +4196,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4219,10 +4216,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4239,10 +4236,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4259,10 +4256,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4279,10 +4276,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4299,10 +4296,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4319,10 +4316,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4334,15 +4331,15 @@
         <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4359,10 +4356,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>295</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4379,10 +4376,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>297</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4399,10 +4396,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4419,10 +4416,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4439,10 +4436,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4459,10 +4456,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>305</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4479,10 +4476,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>307</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4499,10 +4496,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>309</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4519,10 +4516,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>311</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4539,10 +4536,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4559,10 +4556,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4579,10 +4576,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>317</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4599,10 +4596,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>319</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4619,10 +4616,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -4639,10 +4636,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>323</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4659,10 +4656,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>325</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4679,10 +4676,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>327</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4699,10 +4696,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>329</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4714,21 +4711,21 @@
         <v>144</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>333</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>4</v>
@@ -4739,16 +4736,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>8</v>
@@ -4759,16 +4756,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>11</v>
@@ -4779,16 +4776,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>15</v>
@@ -4799,16 +4796,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>18</v>
@@ -4819,16 +4816,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>21</v>
@@ -4839,16 +4836,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>24</v>
@@ -4859,16 +4856,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>27</v>
@@ -4879,16 +4876,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>30</v>
@@ -4899,16 +4896,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>351</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>352</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>4</v>
@@ -4919,16 +4916,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>8</v>
@@ -4939,16 +4936,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -4959,16 +4956,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>15</v>
@@ -4979,36 +4976,36 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>4</v>
@@ -5019,16 +5016,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>8</v>
@@ -5039,36 +5036,36 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>4</v>
@@ -5079,16 +5076,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>374</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
@@ -5099,16 +5096,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
@@ -5119,56 +5116,56 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>15</v>
@@ -5179,16 +5176,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>18</v>
@@ -5199,16 +5196,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>4</v>
@@ -5219,96 +5216,96 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>393</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>396</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>401</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>21</v>
@@ -5319,16 +5316,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>24</v>
@@ -5339,16 +5336,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>27</v>
@@ -5359,16 +5356,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>30</v>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="406">
   <si>
     <t/>
   </si>
@@ -436,13 +436,13 @@
     <t>20140174</t>
   </si>
   <si>
-    <t>BEAR BRAND CLGEN 189</t>
+    <t>BEAR BRAND CO 189 ML</t>
   </si>
   <si>
     <t>10004906</t>
   </si>
   <si>
-    <t>BEAR BRAND STERIL189</t>
+    <t>BEAR BRAND ST 189 ML</t>
   </si>
   <si>
     <t>14</t>
@@ -481,13 +481,13 @@
     <t>20014069</t>
   </si>
   <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>FF UHT F CRM 946 ML</t>
   </si>
   <si>
     <t>20014071</t>
   </si>
   <si>
-    <t>FF UHT CHOCO 946ML</t>
+    <t>FF UHT CHOCO 946 ML</t>
   </si>
   <si>
     <t>20014070</t>
@@ -505,7 +505,7 @@
     <t>20122061</t>
   </si>
   <si>
-    <t>OATSDE O/M B/BLND 1L</t>
+    <t>OATSDE O/M B/BL 1 L</t>
   </si>
   <si>
     <t>10036647</t>
@@ -646,7 +646,7 @@
     <t>LARISST JELY LECI135</t>
   </si>
   <si>
-    <t>,(E-1B)</t>
+    <t>PT,(E-1B)</t>
   </si>
   <si>
     <t>20140066</t>
@@ -742,19 +742,19 @@
     <t>20114495</t>
   </si>
   <si>
-    <t>NESCAFE CPUCCINO 220</t>
+    <t>NSCAFE CPCCN 220 ML</t>
   </si>
   <si>
     <t>20114493</t>
   </si>
   <si>
-    <t>NESCAFE LATTE 220ML</t>
+    <t>NSCAFE LATTE 220 ML</t>
   </si>
   <si>
     <t>20121456</t>
   </si>
   <si>
-    <t>NSCAFE ICE BLACK 220</t>
+    <t>NSCAFE I BLCK 220 ML</t>
   </si>
   <si>
     <t>20123322</t>
@@ -835,9 +835,6 @@
     <t>IDM TEH APEL 350ML</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20015838</t>
   </si>
   <si>
@@ -961,19 +958,19 @@
     <t>20037150</t>
   </si>
   <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
+    <t>KAKI3 JAMBU 320 ML</t>
   </si>
   <si>
     <t>20037144</t>
   </si>
   <si>
-    <t>KAKI3 PENY.LECI 320</t>
+    <t>KAKI3 LECI 320 ML</t>
   </si>
   <si>
     <t>20069199</t>
   </si>
   <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
+    <t>KAKI3 LMN.LM 320 ML</t>
   </si>
   <si>
     <t>20045995</t>
@@ -1120,7 +1117,7 @@
     <t>20069208</t>
   </si>
   <si>
-    <t>LE MINERALE 600ML</t>
+    <t>LE MINERALE 600 ML</t>
   </si>
   <si>
     <t>18</t>
@@ -4171,15 +4168,15 @@
         <v>33</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>274</v>
+        <v>211</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
@@ -4196,10 +4193,10 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>277</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4216,10 +4213,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>280</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4236,10 +4233,10 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4256,10 +4253,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>283</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>284</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4276,10 +4273,10 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>286</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4296,10 +4293,10 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4316,10 +4313,10 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4331,15 +4328,15 @@
         <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>274</v>
+        <v>211</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>291</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4356,10 +4353,10 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="B137" s="1" t="s">
-        <v>294</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4376,10 +4373,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4396,10 +4393,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>297</v>
-      </c>
-      <c r="B139" s="1" t="s">
-        <v>298</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4416,10 +4413,10 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>300</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
@@ -4436,10 +4433,10 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>301</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>302</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
@@ -4456,10 +4453,10 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>304</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
@@ -4476,10 +4473,10 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>306</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
@@ -4496,10 +4493,10 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>307</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>308</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
@@ -4516,10 +4513,10 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>309</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>310</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
@@ -4536,10 +4533,10 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
@@ -4556,10 +4553,10 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
@@ -4576,10 +4573,10 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>316</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
@@ -4596,10 +4593,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>317</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>318</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
@@ -4616,10 +4613,10 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>319</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
@@ -4636,10 +4633,10 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
@@ -4656,10 +4653,10 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>323</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
@@ -4676,10 +4673,10 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>326</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
@@ -4696,10 +4693,10 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>328</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
@@ -4711,21 +4708,21 @@
         <v>144</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>4</v>
@@ -4736,16 +4733,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>8</v>
@@ -4756,16 +4753,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>11</v>
@@ -4776,16 +4773,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>15</v>
@@ -4796,16 +4793,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>18</v>
@@ -4816,16 +4813,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>21</v>
@@ -4836,16 +4833,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>24</v>
@@ -4856,16 +4853,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>27</v>
@@ -4876,16 +4873,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>30</v>
@@ -4896,16 +4893,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>351</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>4</v>
@@ -4916,16 +4913,16 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="C165" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>8</v>
@@ -4936,16 +4933,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
@@ -4956,16 +4953,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>15</v>
@@ -4976,36 +4973,36 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>274</v>
+        <v>211</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>361</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>4</v>
@@ -5016,16 +5013,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>364</v>
-      </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>8</v>
@@ -5036,36 +5033,36 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>370</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>4</v>
@@ -5076,16 +5073,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
@@ -5096,16 +5093,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
@@ -5116,56 +5113,56 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C175" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>274</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B177" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>15</v>
@@ -5176,16 +5173,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>18</v>
@@ -5196,16 +5193,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>387</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>4</v>
@@ -5216,96 +5213,96 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B184" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>21</v>
@@ -5316,16 +5313,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B185" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>402</v>
-      </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>24</v>
@@ -5336,16 +5333,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>27</v>
@@ -5356,16 +5353,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>30</v>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="408">
   <si>
     <t/>
   </si>
@@ -436,13 +436,13 @@
     <t>20140174</t>
   </si>
   <si>
-    <t>BEAR BRAND CO 189 ML</t>
+    <t>BEAR BRAND CLGEN 189</t>
   </si>
   <si>
     <t>10004906</t>
   </si>
   <si>
-    <t>BEAR BRAND ST 189 ML</t>
+    <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
     <t>14</t>
@@ -481,13 +481,13 @@
     <t>20014069</t>
   </si>
   <si>
-    <t>FF UHT F CRM 946 ML</t>
+    <t>FF UHT FULL CRM 946</t>
   </si>
   <si>
     <t>20014071</t>
   </si>
   <si>
-    <t>FF UHT CHOCO 946 ML</t>
+    <t>FF UHT CHOCO 946ML</t>
   </si>
   <si>
     <t>20014070</t>
@@ -505,7 +505,7 @@
     <t>20122061</t>
   </si>
   <si>
-    <t>OATSDE O/M B/BL 1 L</t>
+    <t>OATSDE O/M B/BLND 1L</t>
   </si>
   <si>
     <t>10036647</t>
@@ -742,19 +742,19 @@
     <t>20114495</t>
   </si>
   <si>
-    <t>NSCAFE CPCCN 220 ML</t>
+    <t>NESCAFE CPUCCINO 220</t>
   </si>
   <si>
     <t>20114493</t>
   </si>
   <si>
-    <t>NSCAFE LATTE 220 ML</t>
+    <t>NESCAFE LATTE 220ML</t>
   </si>
   <si>
     <t>20121456</t>
   </si>
   <si>
-    <t>NSCAFE I BLCK 220 ML</t>
+    <t>NSCAFE ICE BLACK 220</t>
   </si>
   <si>
     <t>20123322</t>
@@ -958,19 +958,19 @@
     <t>20037150</t>
   </si>
   <si>
-    <t>KAKI3 JAMBU 320 ML</t>
+    <t>KAKI3 PENY.JAMBU 320</t>
   </si>
   <si>
     <t>20037144</t>
   </si>
   <si>
-    <t>KAKI3 LECI 320 ML</t>
+    <t>KAKI3 PENY.LECI 320</t>
   </si>
   <si>
     <t>20069199</t>
   </si>
   <si>
-    <t>KAKI3 LMN.LM 320 ML</t>
+    <t>KAKI3 LMN.LM KLG 320</t>
   </si>
   <si>
     <t>20045995</t>
@@ -1057,67 +1057,73 @@
     <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
+    <t>20005530</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 1.5</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20137992</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 1600ML</t>
+  </si>
+  <si>
+    <t>20139457</t>
+  </si>
+  <si>
+    <t>AQUVIVA 12X250ML</t>
+  </si>
+  <si>
+    <t>20126648</t>
+  </si>
+  <si>
+    <t>LE MINERALE 6X330ML</t>
+  </si>
+  <si>
+    <t>20094171</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR 24X200</t>
+  </si>
+  <si>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
+  </si>
+  <si>
+    <t>10004337</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR/MN1500</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
     <t>20008785</t>
   </si>
   <si>
     <t>CLUB AIR MNRL 1500ML</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20137992</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 1600ML</t>
-  </si>
-  <si>
-    <t>20139457</t>
-  </si>
-  <si>
-    <t>AQUVIVA 12X250ML</t>
-  </si>
-  <si>
-    <t>20126648</t>
-  </si>
-  <si>
-    <t>LE MINERALE 6X330ML</t>
-  </si>
-  <si>
-    <t>20094171</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR 24X200</t>
-  </si>
-  <si>
-    <t>10000426</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL1500</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
-  </si>
-  <si>
-    <t>10004337</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR/MN1500</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
     <t>20069208</t>
   </si>
   <si>
-    <t>LE MINERALE 600 ML</t>
+    <t>LE MINERALE 600ML</t>
   </si>
   <si>
     <t>18</t>
@@ -1621,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4165,7 +4171,7 @@
         <v>70</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>211</v>
@@ -4905,10 +4911,10 @@
         <v>350</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4925,7 +4931,7 @@
         <v>350</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4945,7 +4951,7 @@
         <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4965,7 +4971,7 @@
         <v>350</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4985,7 +4991,7 @@
         <v>350</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>211</v>
@@ -5062,73 +5068,73 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>211</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5142,13 +5148,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>366</v>
+        <v>211</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5162,13 +5168,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>34</v>
+        <v>366</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5182,10 +5188,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>34</v>
@@ -5202,93 +5208,93 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>389</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5302,13 +5308,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>109</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5322,13 +5328,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5342,13 +5348,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5362,12 +5368,32 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E187" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F187" s="1" t="s">
+      <c r="F188" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="406">
   <si>
     <t/>
   </si>
@@ -353,12 +353,6 @@
   </si>
   <si>
     <t>INDOMILK MELON 190</t>
-  </si>
-  <si>
-    <t>20136816</t>
-  </si>
-  <si>
-    <t>INDOMILK BLUEBERI190</t>
   </si>
   <si>
     <t>20107748</t>
@@ -1627,7 +1621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2611,7 +2605,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
@@ -2628,10 +2622,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>
@@ -2651,7 +2645,7 @@
         <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>34</v>
@@ -2671,7 +2665,7 @@
         <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>34</v>
@@ -2691,7 +2685,7 @@
         <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>34</v>
@@ -2711,7 +2705,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>34</v>
@@ -2731,7 +2725,7 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>34</v>
@@ -2751,7 +2745,7 @@
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>
@@ -2771,7 +2765,7 @@
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>34</v>
@@ -2791,7 +2785,7 @@
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>34</v>
@@ -2811,7 +2805,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>34</v>
@@ -2831,7 +2825,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>34</v>
@@ -2851,7 +2845,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2871,7 +2865,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2879,19 +2873,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2911,7 +2905,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>34</v>
@@ -2931,7 +2925,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2951,7 +2945,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2971,7 +2965,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -2991,7 +2985,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -3011,7 +3005,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -3031,7 +3025,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3051,7 +3045,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3071,7 +3065,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3088,10 +3082,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3111,7 +3105,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3131,7 +3125,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3151,7 +3145,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3171,7 +3165,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3191,7 +3185,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3211,7 +3205,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3231,7 +3225,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3251,7 +3245,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3268,10 +3262,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3291,7 +3285,7 @@
         <v>30</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3311,10 +3305,10 @@
         <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3331,10 +3325,10 @@
         <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3351,10 +3345,10 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3371,7 +3365,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>34</v>
@@ -3391,7 +3385,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>34</v>
@@ -3411,10 +3405,10 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -3431,10 +3425,10 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3448,13 +3442,13 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -3471,10 +3465,10 @@
         <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3491,10 +3485,10 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3511,7 +3505,7 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>34</v>
@@ -3531,18 +3525,18 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3551,10 +3545,10 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3571,10 +3565,10 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3591,10 +3585,10 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>211</v>
+        <v>34</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3611,7 +3605,7 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>34</v>
@@ -3631,7 +3625,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3651,7 +3645,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3671,7 +3665,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3691,7 +3685,7 @@
         <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3711,7 +3705,7 @@
         <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3728,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3751,7 +3745,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3771,7 +3765,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3791,7 +3785,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3811,7 +3805,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>34</v>
@@ -3831,7 +3825,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>34</v>
@@ -3851,10 +3845,10 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3871,7 +3865,7 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>109</v>
@@ -3891,7 +3885,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>109</v>
@@ -3911,10 +3905,10 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3931,7 +3925,7 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>34</v>
@@ -3951,10 +3945,10 @@
         <v>37</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3971,7 +3965,7 @@
         <v>37</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>5</v>
@@ -3988,13 +3982,13 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4011,7 +4005,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4031,7 +4025,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4051,7 +4045,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4071,7 +4065,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4091,7 +4085,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4111,7 +4105,7 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>34</v>
@@ -4131,7 +4125,7 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>34</v>
@@ -4151,10 +4145,10 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4168,13 +4162,13 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>211</v>
+        <v>109</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4191,7 +4185,7 @@
         <v>73</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>109</v>
@@ -4211,10 +4205,10 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4231,7 +4225,7 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>34</v>
@@ -4251,7 +4245,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4271,10 +4265,10 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4291,7 +4285,7 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>109</v>
@@ -4311,10 +4305,10 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>109</v>
+        <v>209</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4331,10 +4325,10 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>211</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4351,7 +4345,7 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>34</v>
@@ -4371,7 +4365,7 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4391,7 +4385,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4411,7 +4405,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4428,13 +4422,13 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4448,13 +4442,13 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -4468,10 +4462,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>34</v>
@@ -4488,13 +4482,13 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4508,10 +4502,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>12</v>
@@ -4528,10 +4522,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
@@ -4548,10 +4542,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4568,13 +4562,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4588,10 +4582,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4608,10 +4602,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4628,10 +4622,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4648,10 +4642,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4668,13 +4662,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4688,50 +4682,50 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>76</v>
+        <v>326</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>144</v>
+        <v>329</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>328</v>
+        <v>34</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>34</v>
@@ -4748,10 +4742,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>34</v>
@@ -4768,10 +4762,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4788,13 +4782,13 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4808,10 +4802,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>12</v>
@@ -4828,10 +4822,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>12</v>
@@ -4848,13 +4842,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4868,10 +4862,10 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4888,30 +4882,30 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>34</v>
@@ -4928,10 +4922,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4948,10 +4942,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4968,13 +4962,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4988,33 +4982,33 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>211</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5028,33 +5022,33 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>34</v>
+        <v>364</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>366</v>
+        <v>109</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5068,73 +5062,73 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>34</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5148,13 +5142,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>211</v>
+        <v>364</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5168,13 +5162,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5188,10 +5182,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>34</v>
@@ -5208,93 +5202,93 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>389</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5308,13 +5302,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>394</v>
+        <v>109</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5328,13 +5322,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5348,13 +5342,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5368,32 +5362,12 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A188" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F188" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="408">
   <si>
     <t/>
   </si>
@@ -1051,13 +1051,19 @@
     <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
+    <t>20099547</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 1500</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>20005530</t>
   </si>
   <si>
     <t>NESTLE PURE LIFE 1.5</t>
-  </si>
-  <si>
-    <t>16</t>
   </si>
   <si>
     <t>20137992</t>
@@ -1621,7 +1627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F187"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4885,7 +4891,7 @@
         <v>348</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>34</v>
@@ -4905,7 +4911,7 @@
         <v>348</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>34</v>
@@ -4925,7 +4931,7 @@
         <v>348</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4945,7 +4951,7 @@
         <v>348</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4965,10 +4971,10 @@
         <v>348</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -4982,33 +4988,33 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>12</v>
+        <v>209</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="C169" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="E169" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5022,33 +5028,33 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>364</v>
+        <v>34</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5062,73 +5068,73 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>372</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5142,13 +5148,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>364</v>
+        <v>209</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5162,13 +5168,13 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>34</v>
+        <v>366</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5182,10 +5188,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>34</v>
@@ -5202,93 +5208,93 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>389</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F181" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F181" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5302,13 +5308,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>109</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5322,13 +5328,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -5342,13 +5348,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5362,12 +5368,32 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E187" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F187" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F187" s="1" t="s">
+      <c r="F188" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -622,6 +622,201 @@
     <t>STRWAY SOYA BEAN 310</t>
   </si>
   <si>
+    <t>10003389</t>
+  </si>
+  <si>
+    <t>KIRANTI SEHAT BLN150</t>
+  </si>
+  <si>
+    <t>20029054</t>
+  </si>
+  <si>
+    <t>KIRANTI JUICE 150ML</t>
+  </si>
+  <si>
+    <t>20137228</t>
+  </si>
+  <si>
+    <t>KIRANTI LYCHEE 150ML</t>
+  </si>
+  <si>
+    <t>20137229</t>
+  </si>
+  <si>
+    <t>KIRANTI BERRY 150ML</t>
+  </si>
+  <si>
+    <t>20140068</t>
+  </si>
+  <si>
+    <t>LARISST JELY LECI135</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140066</t>
+  </si>
+  <si>
+    <t>LARISST JELY MANG135</t>
+  </si>
+  <si>
+    <t>20140067</t>
+  </si>
+  <si>
+    <t>LARISST JELY STRW135</t>
+  </si>
+  <si>
+    <t>20113377</t>
+  </si>
+  <si>
+    <t>FLRDINA COCO BIT 350</t>
+  </si>
+  <si>
+    <t>20043877</t>
+  </si>
+  <si>
+    <t>FLORIDINA ORANGE 350</t>
+  </si>
+  <si>
+    <t>20125638</t>
+  </si>
+  <si>
+    <t>NTRSARI JRK PRS 10'S</t>
+  </si>
+  <si>
+    <t>20026226</t>
+  </si>
+  <si>
+    <t>ULTRA TEH KOTAK 500</t>
+  </si>
+  <si>
+    <t>10036640</t>
+  </si>
+  <si>
+    <t>TEH KOTAK JASMINE300</t>
+  </si>
+  <si>
+    <t>20048435</t>
+  </si>
+  <si>
+    <t>TEH KOTAK LESS/S 300</t>
+  </si>
+  <si>
+    <t>20044334</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BTL TPK300</t>
+  </si>
+  <si>
+    <t>10005128</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK B250</t>
+  </si>
+  <si>
+    <t>20001119</t>
+  </si>
+  <si>
+    <t>SOSRO TEH KOTAK 4+2S</t>
+  </si>
+  <si>
+    <t>20114495</t>
+  </si>
+  <si>
+    <t>NESCAFE CPUCCINO 220</t>
+  </si>
+  <si>
+    <t>20114493</t>
+  </si>
+  <si>
+    <t>NESCAFE LATTE 220ML</t>
+  </si>
+  <si>
+    <t>20121456</t>
+  </si>
+  <si>
+    <t>NSCAFE ICE BLACK 220</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 180</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 180</t>
+  </si>
+  <si>
+    <t>20036157</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 450</t>
+  </si>
+  <si>
+    <t>20037565</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI500</t>
+  </si>
+  <si>
+    <t>20048155</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH L/SGR350</t>
+  </si>
+  <si>
+    <t>20035484</t>
+  </si>
+  <si>
+    <t>PUCUK/H TEH MLATI350</t>
+  </si>
+  <si>
+    <t>20072249</t>
+  </si>
+  <si>
+    <t>SOSRO TEH BOTOL 350</t>
+  </si>
+  <si>
+    <t>20066455</t>
+  </si>
+  <si>
+    <t>FRUIT TEA APPLE 350</t>
+  </si>
+  <si>
+    <t>20066454</t>
+  </si>
+  <si>
+    <t>FRUIT TEA BLCKCR 350</t>
+  </si>
+  <si>
+    <t>20073495</t>
+  </si>
+  <si>
+    <t>FRUIT TEA FREEZE 350</t>
+  </si>
+  <si>
+    <t>20101897</t>
+  </si>
+  <si>
+    <t>IDM TEH APEL 350ML</t>
+  </si>
+  <si>
     <t>20139297</t>
   </si>
   <si>
@@ -632,201 +827,6 @@
   </si>
   <si>
     <t>POP ICE MANGO 5'S</t>
-  </si>
-  <si>
-    <t>20140068</t>
-  </si>
-  <si>
-    <t>LARISST JELY LECI135</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140066</t>
-  </si>
-  <si>
-    <t>LARISST JELY MANG135</t>
-  </si>
-  <si>
-    <t>20140067</t>
-  </si>
-  <si>
-    <t>LARISST JELY STRW135</t>
-  </si>
-  <si>
-    <t>10003389</t>
-  </si>
-  <si>
-    <t>KIRANTI SEHAT BLN150</t>
-  </si>
-  <si>
-    <t>20029054</t>
-  </si>
-  <si>
-    <t>KIRANTI JUICE 150ML</t>
-  </si>
-  <si>
-    <t>20137228</t>
-  </si>
-  <si>
-    <t>KIRANTI LYCHEE 150ML</t>
-  </si>
-  <si>
-    <t>20137229</t>
-  </si>
-  <si>
-    <t>KIRANTI BERRY 150ML</t>
-  </si>
-  <si>
-    <t>20125638</t>
-  </si>
-  <si>
-    <t>NTRSARI JRK PRS 10'S</t>
-  </si>
-  <si>
-    <t>20113377</t>
-  </si>
-  <si>
-    <t>FLRDINA COCO BIT 350</t>
-  </si>
-  <si>
-    <t>20043877</t>
-  </si>
-  <si>
-    <t>FLORIDINA ORANGE 350</t>
-  </si>
-  <si>
-    <t>20026226</t>
-  </si>
-  <si>
-    <t>ULTRA TEH KOTAK 500</t>
-  </si>
-  <si>
-    <t>10036640</t>
-  </si>
-  <si>
-    <t>TEH KOTAK JASMINE300</t>
-  </si>
-  <si>
-    <t>20048435</t>
-  </si>
-  <si>
-    <t>TEH KOTAK LESS/S 300</t>
-  </si>
-  <si>
-    <t>20044334</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BTL TPK300</t>
-  </si>
-  <si>
-    <t>10005128</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK B250</t>
-  </si>
-  <si>
-    <t>20001119</t>
-  </si>
-  <si>
-    <t>SOSRO TEH KOTAK 4+2S</t>
-  </si>
-  <si>
-    <t>20114495</t>
-  </si>
-  <si>
-    <t>NESCAFE CPUCCINO 220</t>
-  </si>
-  <si>
-    <t>20114493</t>
-  </si>
-  <si>
-    <t>NESCAFE LATTE 220ML</t>
-  </si>
-  <si>
-    <t>20121456</t>
-  </si>
-  <si>
-    <t>NSCAFE ICE BLACK 220</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 180</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 180</t>
-  </si>
-  <si>
-    <t>20036157</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 450</t>
-  </si>
-  <si>
-    <t>20037565</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI500</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20072249</t>
-  </si>
-  <si>
-    <t>SOSRO TEH BOTOL 350</t>
-  </si>
-  <si>
-    <t>20066455</t>
-  </si>
-  <si>
-    <t>FRUIT TEA APPLE 350</t>
-  </si>
-  <si>
-    <t>20066454</t>
-  </si>
-  <si>
-    <t>FRUIT TEA BLCKCR 350</t>
-  </si>
-  <si>
-    <t>20073495</t>
-  </si>
-  <si>
-    <t>FRUIT TEA FREEZE 350</t>
-  </si>
-  <si>
-    <t>20101897</t>
-  </si>
-  <si>
-    <t>IDM TEH APEL 350ML</t>
   </si>
   <si>
     <t>20015838</t>
@@ -3534,15 +3534,15 @@
         <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3554,15 +3554,15 @@
         <v>21</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3574,7 +3574,7 @@
         <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3594,7 +3594,7 @@
         <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3614,7 +3614,7 @@
         <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3631,7 +3631,7 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>34</v>
@@ -3651,7 +3651,7 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>34</v>
@@ -3671,7 +3671,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3688,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3708,10 +3708,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>142</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3731,7 +3731,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3751,7 +3751,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3771,7 +3771,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3791,7 +3791,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3811,10 +3811,10 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3831,10 +3831,10 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3851,7 +3851,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>109</v>
@@ -3871,10 +3871,10 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3891,10 +3891,10 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3911,10 +3911,10 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3931,10 +3931,10 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3948,13 +3948,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3968,13 +3968,13 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -3991,7 +3991,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -4011,7 +4011,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4031,7 +4031,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4051,7 +4051,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4071,7 +4071,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4091,7 +4091,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4111,10 +4111,10 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4131,7 +4131,7 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>34</v>
@@ -4151,10 +4151,10 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>209</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4314,7 +4314,7 @@
         <v>27</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4994,7 +4994,7 @@
         <v>21</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -5154,7 +5154,7 @@
         <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="413">
   <si>
     <t/>
   </si>
@@ -310,10 +310,16 @@
     <t>DANCOW FRTGO VNLA110</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>20057229</t>
   </si>
   <si>
-    <t>VIDORAN SUSU COK 110</t>
+    <t>VIDRN XMRT SS COK110</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>20113180</t>
@@ -328,27 +334,33 @@
     <t>MILO ACT-GO 4X180ML</t>
   </si>
   <si>
+    <t>20143400</t>
+  </si>
+  <si>
+    <t>MILO DRNK EXT CHO3+1</t>
+  </si>
+  <si>
+    <t>20087290</t>
+  </si>
+  <si>
+    <t>HILO SCHL UHT CHO200</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20134048</t>
+  </si>
+  <si>
+    <t>HILO PRTEIN CHOCO190</t>
+  </si>
+  <si>
     <t>20130034</t>
   </si>
   <si>
     <t>OATSDE STR BR.BLN200</t>
   </si>
   <si>
-    <t>20087290</t>
-  </si>
-  <si>
-    <t>HILO SCHL UHT CHO200</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20134048</t>
-  </si>
-  <si>
-    <t>HILO PRTEIN CHOCO190</t>
-  </si>
-  <si>
     <t>20053799</t>
   </si>
   <si>
@@ -439,9 +451,6 @@
     <t>BEAR BRAND STERIL189</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>20133540</t>
   </si>
   <si>
@@ -667,6 +676,15 @@
     <t>LARISST JELY STRW135</t>
   </si>
   <si>
+    <t>20143385</t>
+  </si>
+  <si>
+    <t>SUNPRIDE MGOGVA2X220</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
     <t>20113377</t>
   </si>
   <si>
@@ -998,9 +1016,6 @@
   </si>
   <si>
     <t>BUAVITA ORANGE 1L</t>
-  </si>
-  <si>
-    <t>15</t>
   </si>
   <si>
     <t>20067201</t>
@@ -1627,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F188"/>
+  <dimension ref="A1:F190"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2231,7 +2246,7 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>76</v>
@@ -2251,7 +2266,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>34</v>
@@ -2271,7 +2286,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>34</v>
@@ -2291,7 +2306,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>34</v>
@@ -2311,7 +2326,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>34</v>
@@ -2331,7 +2346,7 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -2351,7 +2366,7 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>34</v>
@@ -2371,7 +2386,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>34</v>
@@ -2391,7 +2406,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>34</v>
@@ -2411,7 +2426,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>34</v>
@@ -2431,7 +2446,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>34</v>
@@ -2451,7 +2466,7 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>34</v>
@@ -2459,10 +2474,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2471,7 +2486,7 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>12</v>
@@ -2479,10 +2494,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2499,10 +2514,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2519,10 +2534,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2539,10 +2554,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2554,15 +2569,15 @@
         <v>15</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2579,10 +2594,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2599,10 +2614,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2611,7 +2626,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
@@ -2619,19 +2634,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>
@@ -2639,10 +2654,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2651,7 +2666,7 @@
         <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>34</v>
@@ -2659,10 +2674,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2671,7 +2686,7 @@
         <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>34</v>
@@ -2679,10 +2694,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2691,7 +2706,7 @@
         <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>34</v>
@@ -2699,10 +2714,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2711,7 +2726,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>34</v>
@@ -2719,10 +2734,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2731,7 +2746,7 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>34</v>
@@ -2739,10 +2754,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2751,7 +2766,7 @@
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>
@@ -2759,10 +2774,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2771,7 +2786,7 @@
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>34</v>
@@ -2779,10 +2794,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2791,7 +2806,7 @@
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>34</v>
@@ -2799,10 +2814,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2811,7 +2826,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>34</v>
@@ -2819,10 +2834,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2831,7 +2846,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>34</v>
@@ -2839,10 +2854,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2851,7 +2866,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2859,10 +2874,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2871,7 +2886,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2879,19 +2894,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2899,10 +2914,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2911,7 +2926,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>34</v>
@@ -2919,10 +2934,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2931,7 +2946,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2939,10 +2954,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2951,7 +2966,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2959,10 +2974,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2971,7 +2986,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -2979,10 +2994,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -2991,7 +3006,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -2999,10 +3014,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -3011,7 +3026,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -3019,10 +3034,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -3031,7 +3046,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3039,10 +3054,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3051,7 +3066,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3059,10 +3074,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3071,7 +3086,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3079,19 +3094,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3099,10 +3114,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3111,7 +3126,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3119,10 +3134,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3131,7 +3146,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3139,10 +3154,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3151,7 +3166,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3159,10 +3174,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3171,7 +3186,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3179,10 +3194,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3191,7 +3206,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3199,10 +3214,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3211,7 +3226,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3219,10 +3234,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3231,7 +3246,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3239,10 +3254,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3251,7 +3266,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3259,19 +3274,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3279,10 +3294,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3291,7 +3306,7 @@
         <v>30</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3299,10 +3314,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3311,18 +3326,18 @@
         <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3331,18 +3346,18 @@
         <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3351,18 +3366,18 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3371,7 +3386,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>34</v>
@@ -3379,10 +3394,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3391,7 +3406,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>34</v>
@@ -3399,10 +3414,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3411,18 +3426,18 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3431,38 +3446,38 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3471,18 +3486,18 @@
         <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3491,18 +3506,18 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3511,7 +3526,7 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>34</v>
@@ -3519,10 +3534,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3531,7 +3546,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>34</v>
@@ -3539,10 +3554,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3551,7 +3566,7 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>34</v>
@@ -3559,10 +3574,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3571,10 +3586,10 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3591,18 +3606,18 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
@@ -3611,18 +3626,18 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3631,18 +3646,18 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -3651,18 +3666,18 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>34</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3671,7 +3686,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3679,19 +3694,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3699,19 +3714,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3719,10 +3734,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3731,7 +3746,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3739,10 +3754,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3751,7 +3766,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3759,10 +3774,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3771,7 +3786,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3779,10 +3794,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3791,7 +3806,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3799,10 +3814,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3811,18 +3826,18 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3831,18 +3846,18 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3851,18 +3866,18 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3871,18 +3886,18 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3891,18 +3906,18 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3911,18 +3926,18 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3931,58 +3946,58 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3991,7 +4006,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -3999,10 +4014,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -4011,7 +4026,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4019,10 +4034,10 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -4031,7 +4046,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4039,10 +4054,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -4051,7 +4066,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4059,10 +4074,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -4071,7 +4086,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4079,10 +4094,10 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
@@ -4091,7 +4106,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4099,10 +4114,10 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
@@ -4111,18 +4126,18 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4131,7 +4146,7 @@
         <v>70</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>34</v>
@@ -4139,10 +4154,10 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
@@ -4151,58 +4166,58 @@
         <v>70</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
@@ -4211,18 +4226,18 @@
         <v>73</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
@@ -4231,18 +4246,18 @@
         <v>73</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
@@ -4251,7 +4266,7 @@
         <v>73</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4259,10 +4274,10 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
@@ -4271,18 +4286,18 @@
         <v>73</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
@@ -4291,18 +4306,18 @@
         <v>73</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
@@ -4311,18 +4326,18 @@
         <v>73</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
@@ -4331,18 +4346,18 @@
         <v>73</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
@@ -4351,18 +4366,18 @@
         <v>73</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
@@ -4371,7 +4386,7 @@
         <v>73</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4379,10 +4394,10 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
@@ -4391,7 +4406,7 @@
         <v>73</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4399,10 +4414,10 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
@@ -4411,7 +4426,7 @@
         <v>73</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4419,39 +4434,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>34</v>
@@ -4459,79 +4474,79 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
@@ -4539,19 +4554,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4559,59 +4574,59 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4619,19 +4634,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4639,19 +4654,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4659,62 +4674,62 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>326</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>329</v>
+        <v>99</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4728,30 +4743,30 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>329</v>
+        <v>99</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>34</v>
+        <v>332</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>34</v>
@@ -4759,19 +4774,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4779,59 +4794,59 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>12</v>
@@ -4839,62 +4854,62 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>329</v>
+        <v>102</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>348</v>
+        <v>102</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4908,13 +4923,13 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>348</v>
+        <v>102</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4928,10 +4943,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4939,19 +4954,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C166" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="E166" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4959,19 +4974,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4979,42 +4994,42 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5028,13 +5043,13 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5048,13 +5063,13 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>366</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5068,13 +5083,13 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5088,13 +5103,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5108,27 +5123,27 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>12</v>
+        <v>111</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
@@ -5139,22 +5154,22 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B176" s="1" t="s">
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>213</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5168,73 +5183,73 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>366</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>377</v>
-      </c>
       <c r="E178" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>34</v>
+        <v>371</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5248,73 +5263,73 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>391</v>
+        <v>34</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="C182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>394</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="C184" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="C184" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5328,72 +5343,112 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>109</v>
+        <v>402</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>34</v>
+        <v>399</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E188" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F188" s="1" t="s">
+      <c r="F190" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="410">
   <si>
     <t/>
   </si>
@@ -211,12 +211,6 @@
     <t>INDOMLK KID F.CRM115</t>
   </si>
   <si>
-    <t>20136817</t>
-  </si>
-  <si>
-    <t>INDOMLK KID BNANA115</t>
-  </si>
-  <si>
     <t>20112746</t>
   </si>
   <si>
@@ -340,6 +334,9 @@
     <t>MILO DRNK EXT CHO3+1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>20087290</t>
   </si>
   <si>
@@ -661,9 +658,6 @@
     <t>LARISST JELY LECI135</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20140066</t>
   </si>
   <si>
@@ -680,9 +674,6 @@
   </si>
   <si>
     <t>SUNPRIDE MGOGVA2X220</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
   </si>
   <si>
     <t>20113377</t>
@@ -1642,7 +1633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2186,7 +2177,7 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>34</v>
@@ -2194,10 +2185,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -2206,7 +2197,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>34</v>
@@ -2214,30 +2205,30 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -2246,10 +2237,10 @@
         <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2266,7 +2257,7 @@
         <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>34</v>
@@ -2286,7 +2277,7 @@
         <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>34</v>
@@ -2306,7 +2297,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>34</v>
@@ -2326,7 +2317,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>34</v>
@@ -2346,7 +2337,7 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>34</v>
@@ -2366,7 +2357,7 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>34</v>
@@ -2386,7 +2377,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>34</v>
@@ -2406,7 +2397,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>34</v>
@@ -2426,7 +2417,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>34</v>
@@ -2446,7 +2437,7 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>34</v>
@@ -2454,10 +2445,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2466,30 +2457,30 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2506,7 +2497,7 @@
         <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>34</v>
@@ -2526,18 +2517,18 @@
         <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2546,18 +2537,18 @@
         <v>18</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2566,18 +2557,18 @@
         <v>18</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2586,7 +2577,7 @@
         <v>18</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>34</v>
@@ -2594,10 +2585,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2606,7 +2597,7 @@
         <v>18</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>34</v>
@@ -2614,10 +2605,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2626,7 +2617,7 @@
         <v>18</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>34</v>
@@ -2634,19 +2625,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>34</v>
@@ -2654,10 +2645,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2666,7 +2657,7 @@
         <v>21</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>34</v>
@@ -2674,10 +2665,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2686,7 +2677,7 @@
         <v>21</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>34</v>
@@ -2694,10 +2685,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2706,7 +2697,7 @@
         <v>21</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>34</v>
@@ -2714,10 +2705,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2726,7 +2717,7 @@
         <v>21</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>34</v>
@@ -2734,10 +2725,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
@@ -2746,7 +2737,7 @@
         <v>21</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>34</v>
@@ -2754,10 +2745,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
@@ -2766,7 +2757,7 @@
         <v>21</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>34</v>
@@ -2774,10 +2765,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
@@ -2786,7 +2777,7 @@
         <v>21</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>34</v>
@@ -2794,10 +2785,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
@@ -2806,7 +2797,7 @@
         <v>21</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>34</v>
@@ -2814,10 +2805,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
@@ -2826,7 +2817,7 @@
         <v>21</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>34</v>
@@ -2834,10 +2825,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2846,7 +2837,7 @@
         <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>34</v>
@@ -2854,10 +2845,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
@@ -2866,7 +2857,7 @@
         <v>21</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>34</v>
@@ -2874,10 +2865,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
@@ -2886,7 +2877,7 @@
         <v>21</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>34</v>
@@ -2894,19 +2885,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>34</v>
@@ -2914,10 +2905,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
@@ -2926,7 +2917,7 @@
         <v>24</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>34</v>
@@ -2934,10 +2925,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
@@ -2946,7 +2937,7 @@
         <v>24</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>34</v>
@@ -2954,10 +2945,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
@@ -2966,7 +2957,7 @@
         <v>24</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>34</v>
@@ -2974,10 +2965,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
@@ -2986,7 +2977,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>34</v>
@@ -2994,10 +2985,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
@@ -3006,7 +2997,7 @@
         <v>24</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>34</v>
@@ -3014,10 +3005,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -3026,7 +3017,7 @@
         <v>24</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>34</v>
@@ -3034,10 +3025,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -3046,7 +3037,7 @@
         <v>24</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>34</v>
@@ -3054,10 +3045,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
@@ -3066,7 +3057,7 @@
         <v>24</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>34</v>
@@ -3074,10 +3065,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
@@ -3086,7 +3077,7 @@
         <v>24</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>34</v>
@@ -3094,19 +3085,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>34</v>
@@ -3114,10 +3105,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
@@ -3126,7 +3117,7 @@
         <v>27</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>34</v>
@@ -3134,10 +3125,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
@@ -3146,7 +3137,7 @@
         <v>27</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>34</v>
@@ -3154,10 +3145,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
@@ -3166,7 +3157,7 @@
         <v>27</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>34</v>
@@ -3174,10 +3165,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
@@ -3186,7 +3177,7 @@
         <v>27</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>34</v>
@@ -3194,10 +3185,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
@@ -3206,7 +3197,7 @@
         <v>27</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>34</v>
@@ -3214,10 +3205,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
@@ -3226,7 +3217,7 @@
         <v>27</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>34</v>
@@ -3234,10 +3225,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
@@ -3246,7 +3237,7 @@
         <v>27</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>34</v>
@@ -3254,10 +3245,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
@@ -3266,7 +3257,7 @@
         <v>27</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>34</v>
@@ -3274,19 +3265,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>34</v>
@@ -3294,10 +3285,10 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
@@ -3306,7 +3297,7 @@
         <v>30</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>34</v>
@@ -3314,10 +3305,10 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
@@ -3326,18 +3317,18 @@
         <v>30</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
@@ -3346,18 +3337,18 @@
         <v>30</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
@@ -3366,18 +3357,18 @@
         <v>30</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -3386,7 +3377,7 @@
         <v>30</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>34</v>
@@ -3394,10 +3385,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3406,7 +3397,7 @@
         <v>30</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>34</v>
@@ -3414,10 +3405,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3426,18 +3417,18 @@
         <v>30</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3446,38 +3437,38 @@
         <v>30</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3486,18 +3477,18 @@
         <v>33</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3506,18 +3497,18 @@
         <v>33</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3526,7 +3517,7 @@
         <v>33</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>34</v>
@@ -3534,10 +3525,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3546,7 +3537,7 @@
         <v>33</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>34</v>
@@ -3554,10 +3545,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3566,7 +3557,7 @@
         <v>33</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>34</v>
@@ -3574,10 +3565,10 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
@@ -3586,18 +3577,18 @@
         <v>33</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>3</v>
@@ -3606,10 +3597,10 @@
         <v>33</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>216</v>
+        <v>107</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3626,10 +3617,10 @@
         <v>33</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>216</v>
+        <v>107</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3646,10 +3637,10 @@
         <v>33</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>216</v>
+        <v>34</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3666,18 +3657,18 @@
         <v>33</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>223</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>225</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
@@ -3686,7 +3677,7 @@
         <v>33</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>34</v>
@@ -3694,10 +3685,10 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>227</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3706,7 +3697,7 @@
         <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3714,19 +3705,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>229</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3734,10 +3725,10 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
@@ -3746,7 +3737,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3754,10 +3745,10 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
@@ -3766,7 +3757,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3774,10 +3765,10 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>235</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
@@ -3786,7 +3777,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3794,10 +3785,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3806,7 +3797,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3814,10 +3805,10 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>239</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
@@ -3826,7 +3817,7 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>34</v>
@@ -3834,10 +3825,10 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -3846,18 +3837,18 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -3866,18 +3857,18 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>245</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -3886,18 +3877,18 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -3906,18 +3897,18 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -3926,7 +3917,7 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>34</v>
@@ -3934,10 +3925,10 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -3946,18 +3937,18 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -3966,7 +3957,7 @@
         <v>37</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3974,39 +3965,39 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -4014,19 +4005,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B119" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4034,19 +4025,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4054,19 +4045,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B121" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4074,19 +4065,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4094,19 +4085,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B123" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4114,19 +4105,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>34</v>
@@ -4134,59 +4125,59 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B125" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C126" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>216</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B127" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>34</v>
@@ -4194,79 +4185,79 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B128" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B131" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B131" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>34</v>
@@ -4274,19 +4265,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B132" s="1" t="s">
-        <v>285</v>
-      </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>34</v>
@@ -4294,99 +4285,99 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B135" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>216</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B137" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B137" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4394,19 +4385,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4414,19 +4405,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B139" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4434,19 +4425,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4454,59 +4445,59 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B141" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B143" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B143" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>34</v>
@@ -4514,39 +4505,39 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B144" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B144" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B145" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B145" s="1" t="s">
-        <v>311</v>
-      </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>12</v>
@@ -4554,19 +4545,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="C146" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>12</v>
@@ -4574,19 +4565,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>12</v>
@@ -4594,39 +4585,39 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>317</v>
-      </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B149" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -4634,19 +4625,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B150" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>5</v>
@@ -4654,19 +4645,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4674,19 +4665,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>5</v>
@@ -4694,42 +4685,42 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B153" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F154" s="1" t="s">
         <v>329</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4743,30 +4734,30 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>332</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>34</v>
@@ -4774,19 +4765,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B157" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>34</v>
@@ -4794,19 +4785,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>34</v>
@@ -4814,39 +4805,39 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>340</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>12</v>
@@ -4854,19 +4845,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>12</v>
@@ -4874,39 +4865,39 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B163" s="1" t="s">
-        <v>348</v>
-      </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4914,22 +4905,22 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B164" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="C164" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -4943,10 +4934,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4954,19 +4945,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4974,19 +4965,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4994,19 +4985,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B168" s="1" t="s">
-        <v>359</v>
-      </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>34</v>
@@ -5014,42 +5005,42 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B169" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="B169" s="1" t="s">
-        <v>361</v>
-      </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>216</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5063,33 +5054,33 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="C172" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5103,33 +5094,33 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>371</v>
+        <v>110</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="B174" s="1" t="s">
+      <c r="C174" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="C174" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D174" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="E174" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5149,7 +5140,7 @@
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -5169,7 +5160,7 @@
         <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5183,70 +5174,70 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>216</v>
+        <v>368</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>371</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>34</v>
@@ -5254,22 +5245,22 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B181" s="1" t="s">
+      <c r="C181" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5283,13 +5274,13 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F182" s="1" t="s">
         <v>393</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
@@ -5303,10 +5294,10 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>396</v>
@@ -5323,10 +5314,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>399</v>
@@ -5343,112 +5334,92 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B186" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>399</v>
+        <v>110</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B187" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>111</v>
+        <v>34</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>410</v>
-      </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F190" s="1" t="s">
         <v>34</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="416">
   <si>
     <t/>
   </si>
@@ -850,6 +850,30 @@
     <t>POCARI SWEAT 500ML</t>
   </si>
   <si>
+    <t>20142818</t>
+  </si>
+  <si>
+    <t>EWATER GRAPEFRT 555</t>
+  </si>
+  <si>
+    <t>20142819</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 555ML</t>
+  </si>
+  <si>
+    <t>20142862</t>
+  </si>
+  <si>
+    <t>EWATER GRPFRT 380</t>
+  </si>
+  <si>
+    <t>20142863</t>
+  </si>
+  <si>
+    <t>EWATER LEMON 380</t>
+  </si>
+  <si>
     <t>20019674</t>
   </si>
   <si>
@@ -862,177 +886,171 @@
     <t>YOU C1000 LMN WTR500</t>
   </si>
   <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20002504</t>
+  </si>
+  <si>
+    <t>ADEM SARI BOX 5'S</t>
+  </si>
+  <si>
+    <t>20141508</t>
+  </si>
+  <si>
+    <t>KRTINGDAENG BDD3X150</t>
+  </si>
+  <si>
+    <t>20121348</t>
+  </si>
+  <si>
+    <t>LASEGAR TWST J-L 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20055226</t>
+  </si>
+  <si>
+    <t>NTRIVE/B  STRWBRY100</t>
+  </si>
+  <si>
+    <t>20082247</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL ORG 100</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20115157</t>
+  </si>
+  <si>
+    <t>BUAVITA ORANGE 1L</t>
+  </si>
+  <si>
+    <t>20067201</t>
+  </si>
+  <si>
+    <t>BUAVITA MANGO TPK 1L</t>
+  </si>
+  <si>
+    <t>20067200</t>
+  </si>
+  <si>
+    <t>BUAVITA GUAVA TPK 1L</t>
+  </si>
+  <si>
+    <t>20116490</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 1L</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
     <t>20053540</t>
   </si>
   <si>
     <t>ADEM SARI CK BTL 350</t>
   </si>
   <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20002504</t>
-  </si>
-  <si>
-    <t>ADEM SARI BOX 5'S</t>
-  </si>
-  <si>
-    <t>20141508</t>
-  </si>
-  <si>
-    <t>KRTINGDAENG BDD3X150</t>
-  </si>
-  <si>
-    <t>20121348</t>
-  </si>
-  <si>
-    <t>LASEGAR TWST J-L 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20055226</t>
-  </si>
-  <si>
-    <t>NTRIVE/B  STRWBRY100</t>
-  </si>
-  <si>
-    <t>20082247</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL ORG 100</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20115157</t>
-  </si>
-  <si>
-    <t>BUAVITA ORANGE 1L</t>
-  </si>
-  <si>
-    <t>20067201</t>
-  </si>
-  <si>
-    <t>BUAVITA MANGO TPK 1L</t>
-  </si>
-  <si>
-    <t>20067200</t>
-  </si>
-  <si>
-    <t>BUAVITA GUAVA TPK 1L</t>
-  </si>
-  <si>
-    <t>20116490</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 1L</t>
-  </si>
-  <si>
-    <t>20127835</t>
-  </si>
-  <si>
-    <t>ALANG SARI JN 300ML</t>
-  </si>
-  <si>
     <t>20130801</t>
   </si>
   <si>
@@ -1045,147 +1063,165 @@
     <t>C/BDK PENYEGAR 500ML</t>
   </si>
   <si>
+    <t>20099547</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 1500</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20005530</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 1.5</t>
+  </si>
+  <si>
+    <t>20137992</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 1600ML</t>
+  </si>
+  <si>
+    <t>20139457</t>
+  </si>
+  <si>
+    <t>AQUVIVA 12X250ML</t>
+  </si>
+  <si>
+    <t>20126648</t>
+  </si>
+  <si>
+    <t>LE MINERALE 6X330ML</t>
+  </si>
+  <si>
+    <t>20094171</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR 24X200</t>
+  </si>
+  <si>
+    <t>10000426</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL1500</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20085988</t>
+  </si>
+  <si>
+    <t>LE MINERALE 1500ML</t>
+  </si>
+  <si>
+    <t>10004337</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR/MN1500</t>
+  </si>
+  <si>
+    <t>PT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20008785</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRL 1500ML</t>
+  </si>
+  <si>
+    <t>20069208</t>
+  </si>
+  <si>
+    <t>LE MINERALE 600ML</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTALIN BTL 600mL</t>
+  </si>
+  <si>
+    <t>10003814</t>
+  </si>
+  <si>
+    <t>AQUA AIR MINERAL 600</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20137991</t>
+  </si>
+  <si>
+    <t>AQUVIVA BTL 700ML</t>
+  </si>
+  <si>
+    <t>20141623</t>
+  </si>
+  <si>
+    <t>IDM AIR BDD 6X500ML</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20142495</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN 1L</t>
+  </si>
+  <si>
+    <t>10004336</t>
+  </si>
+  <si>
+    <t>INDOMARET AIR MIN600</t>
+  </si>
+  <si>
+    <t>20005529</t>
+  </si>
+  <si>
+    <t>NESTLE PURE LIFE 600</t>
+  </si>
+  <si>
+    <t>20037131</t>
+  </si>
+  <si>
+    <t>PRIM-A AIR MNRAL 600</t>
+  </si>
+  <si>
+    <t>20008767</t>
+  </si>
+  <si>
+    <t>CLUB AIR MNRAL 600ML</t>
+  </si>
+  <si>
     <t>20134246</t>
   </si>
   <si>
     <t>KAKI3 PENYEGAR 350ML</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>20037153</t>
   </si>
   <si>
     <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
-    <t>20099547</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 1500</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20005530</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 1.5</t>
-  </si>
-  <si>
-    <t>20137992</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 1600ML</t>
-  </si>
-  <si>
-    <t>20139457</t>
-  </si>
-  <si>
-    <t>AQUVIVA 12X250ML</t>
-  </si>
-  <si>
-    <t>20126648</t>
-  </si>
-  <si>
-    <t>LE MINERALE 6X330ML</t>
-  </si>
-  <si>
-    <t>20094171</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR 24X200</t>
-  </si>
-  <si>
-    <t>10000426</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL1500</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20085988</t>
-  </si>
-  <si>
-    <t>LE MINERALE 1500ML</t>
-  </si>
-  <si>
-    <t>10004337</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR/MN1500</t>
-  </si>
-  <si>
-    <t>PT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20008785</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRL 1500ML</t>
-  </si>
-  <si>
-    <t>20069208</t>
-  </si>
-  <si>
-    <t>LE MINERALE 600ML</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>10003814</t>
-  </si>
-  <si>
-    <t>AQUA AIR MINERAL 600</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20141623</t>
-  </si>
-  <si>
-    <t>IDM AIR BDD 6X500ML</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20142495</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN 1L</t>
-  </si>
-  <si>
-    <t>10004336</t>
-  </si>
-  <si>
-    <t>INDOMARET AIR MIN600</t>
-  </si>
-  <si>
-    <t>20137991</t>
-  </si>
-  <si>
-    <t>AQUVIVA BTL 700ML</t>
-  </si>
-  <si>
-    <t>20090527</t>
-  </si>
-  <si>
-    <t>CRYSTALIN BTL 600mL</t>
-  </si>
-  <si>
     <t>10015532</t>
   </si>
   <si>
     <t>AQUA AIR MINERAL 330</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>20045052</t>
   </si>
   <si>
@@ -1223,24 +1259,6 @@
   </si>
   <si>
     <t>PRISTINE 8.6+ BTL600</t>
-  </si>
-  <si>
-    <t>20037131</t>
-  </si>
-  <si>
-    <t>PRIM-A AIR MNRAL 600</t>
-  </si>
-  <si>
-    <t>20008767</t>
-  </si>
-  <si>
-    <t>CLUB AIR MNRAL 600ML</t>
-  </si>
-  <si>
-    <t>20005529</t>
-  </si>
-  <si>
-    <t>NESTLE PURE LIFE 600</t>
   </si>
 </sst>
 </file>
@@ -1633,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F189"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4300,7 +4318,7 @@
         <v>21</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4320,7 +4338,7 @@
         <v>24</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4340,7 +4358,7 @@
         <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4357,7 +4375,7 @@
         <v>71</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>34</v>
@@ -4377,7 +4395,7 @@
         <v>71</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>34</v>
@@ -4397,7 +4415,7 @@
         <v>71</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>34</v>
@@ -4417,7 +4435,7 @@
         <v>71</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>34</v>
@@ -4437,7 +4455,7 @@
         <v>71</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>34</v>
@@ -4820,7 +4838,7 @@
         <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4840,7 +4858,7 @@
         <v>21</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>12</v>
+        <v>110</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4860,7 +4878,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4880,7 +4898,7 @@
         <v>27</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4900,7 +4918,7 @@
         <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -4914,30 +4932,30 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4954,10 +4972,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4974,10 +4992,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -4994,10 +5012,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>34</v>
@@ -5014,13 +5032,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5034,33 +5052,33 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B171" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,33 +5092,33 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>368</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F173" s="1" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5114,50 +5132,50 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B175" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B175" s="1" t="s">
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>34</v>
@@ -5165,59 +5183,59 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B178" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>383</v>
-      </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>368</v>
+        <v>34</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>379</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>34</v>
@@ -5234,13 +5252,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5254,173 +5272,233 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>12</v>
+        <v>370</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>393</v>
+        <v>34</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>396</v>
+        <v>34</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>399</v>
+        <v>110</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>396</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>110</v>
+        <v>405</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F189" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B189" s="1" t="s">
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>34</v>
+      <c r="B190" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -715,7 +715,7 @@
     <t>20044334</t>
   </si>
   <si>
-    <t>SOSRO TEH BTL TPK300</t>
+    <t>SOSRO TEH KTK 300 ML</t>
   </si>
   <si>
     <t>10005128</t>
@@ -1135,7 +1135,7 @@
     <t>20069208</t>
   </si>
   <si>
-    <t>LE MINERALE 600ML</t>
+    <t>LE MINERALE 600 ML</t>
   </si>
   <si>
     <t>18</t>
@@ -1150,7 +1150,7 @@
     <t>10003814</t>
   </si>
   <si>
-    <t>AQUA AIR MINERAL 600</t>
+    <t>AQUA AIR MIN 600 ML</t>
   </si>
   <si>
     <t>19</t>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -1201,19 +1201,19 @@
     <t>CLUB AIR MNRAL 600ML</t>
   </si>
   <si>
+    <t>20037153</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 500ML</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>20134246</t>
   </si>
   <si>
     <t>KAKI3 PENYEGAR 350ML</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20037153</t>
-  </si>
-  <si>
-    <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
     <t>10015532</t>
